--- a/docs/sample-output/05-medical-office/estimate.xlsx
+++ b/docs/sample-output/05-medical-office/estimate.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="342">
   <si>
     <t>FINISHES SOLUTIONS</t>
   </si>
   <si>
-    <t>Total Project Cost — Summary   ·   Desert Ridge MOB · Total $33,869,764</t>
+    <t>Total Project Cost — Summary   ·   Desert Ridge MOB · Total $33,836,122</t>
   </si>
   <si>
     <t>COST SUMMARY</t>
@@ -90,7 +90,7 @@
     <t>Research data version</t>
   </si>
   <si>
-    <t>2026.7c60a42879</t>
+    <t>2026.0c737c8255</t>
   </si>
   <si>
     <t>Engine</t>
@@ -99,10 +99,10 @@
     <t>budget-engine-2.0.0</t>
   </si>
   <si>
-    <t>All defaults come from the research data shipped with the app (2026.7c60a42879), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
-  </si>
-  <si>
-    <t>Cost by Component   ·   Desert Ridge MOB · Total $33,869,764</t>
+    <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
+  </si>
+  <si>
+    <t>Cost by Component   ·   Desert Ridge MOB · Total $33,836,122</t>
   </si>
   <si>
     <t>Component</t>
@@ -144,7 +144,7 @@
     <t>within ($261–$1,202)</t>
   </si>
   <si>
-    <t>Cost by Phase   ·   Desert Ridge MOB · Total $33,869,764</t>
+    <t>Cost by Phase   ·   Desert Ridge MOB · Total $33,836,122</t>
   </si>
   <si>
     <t>Phase</t>
@@ -186,7 +186,7 @@
     <t>6.3%</t>
   </si>
   <si>
-    <t>Line-Item Detail   ·   Desert Ridge MOB · Total $33,869,764</t>
+    <t>Line-Item Detail   ·   Desert Ridge MOB · Total $33,836,122</t>
   </si>
   <si>
     <t>Group</t>
@@ -459,7 +459,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Draw Schedules   ·   Desert Ridge MOB · Total $33,869,764</t>
+    <t>Draw Schedules   ·   Desert Ridge MOB · Total $33,836,122</t>
   </si>
   <si>
     <t>PHASE 1 — MONTHLY DRAWS</t>
@@ -534,7 +534,7 @@
     <t>2028-11</t>
   </si>
   <si>
-    <t>Sources &amp; Assumptions   ·   Desert Ridge MOB · Total $33,869,764</t>
+    <t>Sources &amp; Assumptions   ·   Desert Ridge MOB · Total $33,836,122</t>
   </si>
   <si>
     <t>ASSUMPTIONS</t>
@@ -570,7 +570,7 @@
     <t>LTC 60%, rate 7.00%, fee 1.00%</t>
   </si>
   <si>
-    <t>SOURCES (40)</t>
+    <t>SOURCES (41)</t>
   </si>
   <si>
     <t>Ref</t>
@@ -1027,6 +1027,21 @@
   </si>
   <si>
     <t>https://www.kirksey.com/CMSPages/GetFile.aspx?guid=1c8a21ff-de0e-4629-b9b0-7f38f62c502b</t>
+  </si>
+  <si>
+    <t>residential/single-family.json#e10</t>
+  </si>
+  <si>
+    <t>Cost of Constructing a Home-2024 (Special Study for Housing Economics)</t>
+  </si>
+  <si>
+    <t>National Association of Home Builders (Eric Lynch)</t>
+  </si>
+  <si>
+    <t>26747 USD/unit (2024)</t>
+  </si>
+  <si>
+    <t>https://nahb.org/-/media/AB4EFC742624475A97A0A62189986FF8.ashx</t>
   </si>
 </sst>
 </file>
@@ -1616,7 +1631,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>4335069.39</v>
+        <v>4335069.390000001</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1624,7 +1639,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <v>358557.98</v>
+        <v>329125.96</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1632,7 +1647,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>1158836.04</v>
+        <v>1157599.9</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1640,7 +1655,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>1048427.3</v>
+        <v>1046924.57</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1648,7 +1663,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>232298.04</v>
+        <v>230826.43</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1656,7 +1671,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>7133188.75</v>
+        <v>7099546.25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1672,7 +1687,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>33869764.37</v>
+        <v>33836121.87</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1711,7 +1726,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5">
-        <v>8279275.734888888</v>
+        <v>8271052.012666666</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1839,19 +1854,19 @@
         <v>24044975.62</v>
       </c>
       <c r="E5" s="13">
-        <v>7133188.75</v>
+        <v>7099546.25</v>
       </c>
       <c r="F5" s="13">
         <v>2691600</v>
       </c>
       <c r="G5" s="13">
-        <v>33869764.37</v>
+        <v>33836121.87</v>
       </c>
       <c r="H5" s="13">
-        <v>752.6614304444444</v>
+        <v>751.9138193333333</v>
       </c>
       <c r="I5" s="14">
-        <v>752.6614304444444</v>
+        <v>751.9138193333333</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>41</v>
@@ -1867,13 +1882,13 @@
         <v>24044975.62</v>
       </c>
       <c r="E6" s="16">
-        <v>7133188.75</v>
+        <v>7099546.25</v>
       </c>
       <c r="F6" s="16">
         <v>2691600</v>
       </c>
       <c r="G6" s="16">
-        <v>33869764.37</v>
+        <v>33836121.87</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -1989,19 +2004,19 @@
         <v>24044975.62</v>
       </c>
       <c r="G5" s="13">
-        <v>7133188.75</v>
+        <v>7099546.25</v>
       </c>
       <c r="H5" s="13">
         <v>2691600</v>
       </c>
       <c r="I5" s="13">
-        <v>33869764.37</v>
+        <v>33836121.87</v>
       </c>
       <c r="J5" s="13">
-        <v>20321858.62</v>
+        <v>20301673.12</v>
       </c>
       <c r="K5" s="13">
-        <v>845208.71</v>
+        <v>843907.84</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2016,13 +2031,13 @@
         <v>24044975.62</v>
       </c>
       <c r="G6" s="16">
-        <v>7133188.75</v>
+        <v>7099546.25</v>
       </c>
       <c r="H6" s="16">
         <v>2691600</v>
       </c>
       <c r="I6" s="16">
-        <v>33869764.37</v>
+        <v>33836121.87</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -3131,10 +3146,10 @@
         <v>131</v>
       </c>
       <c r="H39" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I39" s="13">
-        <v>54429.53</v>
+        <v>38331.23</v>
       </c>
       <c r="J39" s="12" t="s">
         <v>68</v>
@@ -3163,10 +3178,10 @@
         <v>131</v>
       </c>
       <c r="H40" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I40" s="13">
-        <v>51664.95</v>
+        <v>38331.23</v>
       </c>
       <c r="J40" s="12" t="s">
         <v>68</v>
@@ -3196,7 +3211,7 @@
       </c>
       <c r="H41" s="18"/>
       <c r="I41" s="13">
-        <v>232298.04</v>
+        <v>230826.43</v>
       </c>
       <c r="J41" s="12" t="s">
         <v>68</v>
@@ -3342,7 +3357,7 @@
       </c>
       <c r="H46" s="18"/>
       <c r="I46" s="13">
-        <v>1158836.04</v>
+        <v>1157599.9</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>68</v>
@@ -3370,7 +3385,7 @@
       </c>
       <c r="H47" s="18"/>
       <c r="I47" s="13">
-        <v>845208.71</v>
+        <v>843907.84</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>68</v>
@@ -3398,7 +3413,7 @@
       </c>
       <c r="H48" s="18"/>
       <c r="I48" s="13">
-        <v>203218.59</v>
+        <v>203016.73</v>
       </c>
       <c r="J48" s="12" t="s">
         <v>68</v>
@@ -3418,7 +3433,7 @@
       <c r="G49" s="15"/>
       <c r="H49" s="15"/>
       <c r="I49" s="16">
-        <v>33869764.37</v>
+        <v>33836121.87</v>
       </c>
       <c r="J49" s="15"/>
     </row>
@@ -3517,13 +3532,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="13">
-        <v>2864553.6</v>
+        <v>2835121.58</v>
       </c>
       <c r="D6" s="13">
         <v>2691600</v>
       </c>
       <c r="E6" s="13">
-        <v>5759372.19</v>
+        <v>5729738.31</v>
       </c>
       <c r="F6" s="13">
         <v>0</v>
@@ -3543,13 +3558,13 @@
         <v>148016.77</v>
       </c>
       <c r="C7" s="13">
-        <v>161010.39</v>
+        <v>160875.01</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="13">
-        <v>309027.16</v>
+        <v>308891.78</v>
       </c>
       <c r="F7" s="13">
         <v>0</v>
@@ -3569,13 +3584,13 @@
         <v>440405.65</v>
       </c>
       <c r="C8" s="13">
-        <v>161010.39</v>
+        <v>160875.01</v>
       </c>
       <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="13">
-        <v>601416.04</v>
+        <v>601280.66</v>
       </c>
       <c r="F8" s="13">
         <v>0</v>
@@ -3595,13 +3610,13 @@
         <v>721950.29</v>
       </c>
       <c r="C9" s="13">
-        <v>161010.39</v>
+        <v>160875</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
       </c>
       <c r="E9" s="13">
-        <v>882960.68</v>
+        <v>882825.29</v>
       </c>
       <c r="F9" s="13">
         <v>0</v>
@@ -3621,13 +3636,13 @@
         <v>985718.15</v>
       </c>
       <c r="C10" s="13">
-        <v>161010.4</v>
+        <v>160875.02</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
       </c>
       <c r="E10" s="13">
-        <v>1146728.55</v>
+        <v>1146593.17</v>
       </c>
       <c r="F10" s="13">
         <v>0</v>
@@ -3647,13 +3662,13 @@
         <v>1225214.31</v>
       </c>
       <c r="C11" s="13">
-        <v>161010.39</v>
+        <v>160875</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
       </c>
       <c r="E11" s="13">
-        <v>1386224.7</v>
+        <v>1386089.31</v>
       </c>
       <c r="F11" s="13">
         <v>0</v>
@@ -3673,13 +3688,13 @@
         <v>1434541.62</v>
       </c>
       <c r="C12" s="13">
-        <v>161010.39</v>
+        <v>160875</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
       </c>
       <c r="E12" s="13">
-        <v>1595552.01</v>
+        <v>1595416.62</v>
       </c>
       <c r="F12" s="13">
         <v>0</v>
@@ -3699,13 +3714,13 @@
         <v>1608545.76</v>
       </c>
       <c r="C13" s="13">
-        <v>161010.37</v>
+        <v>160874.98</v>
       </c>
       <c r="D13" s="13">
         <v>0</v>
       </c>
       <c r="E13" s="13">
-        <v>1769556.13</v>
+        <v>1769420.74</v>
       </c>
       <c r="F13" s="13">
         <v>0</v>
@@ -3725,22 +3740,22 @@
         <v>1742942.17</v>
       </c>
       <c r="C14" s="13">
-        <v>161010.44</v>
+        <v>160875.05</v>
       </c>
       <c r="D14" s="13">
         <v>0</v>
       </c>
       <c r="E14" s="13">
-        <v>97068.29</v>
+        <v>114192.87</v>
       </c>
       <c r="F14" s="13">
-        <v>1806884.32</v>
+        <v>1789624.35</v>
       </c>
       <c r="G14" s="13">
         <v>0</v>
       </c>
       <c r="H14" s="13">
-        <v>1806884.32</v>
+        <v>1789624.35</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3751,7 +3766,7 @@
         <v>1834421.63</v>
       </c>
       <c r="C15" s="13">
-        <v>161010.36</v>
+        <v>160874.97</v>
       </c>
       <c r="D15" s="13">
         <v>0</v>
@@ -3760,13 +3775,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <v>1995431.99</v>
+        <v>1995296.6</v>
       </c>
       <c r="G15" s="13">
-        <v>10540.16</v>
+        <v>10439.48</v>
       </c>
       <c r="H15" s="13">
-        <v>3812856.47</v>
+        <v>3795360.43</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3777,7 +3792,7 @@
         <v>1880731.48</v>
       </c>
       <c r="C16" s="13">
-        <v>161010.36</v>
+        <v>160874.97</v>
       </c>
       <c r="D16" s="13">
         <v>0</v>
@@ -3786,13 +3801,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>2041741.84</v>
+        <v>2041606.45</v>
       </c>
       <c r="G16" s="13">
-        <v>22241.66</v>
+        <v>22139.6</v>
       </c>
       <c r="H16" s="13">
-        <v>5876839.97</v>
+        <v>5859106.48</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3803,7 +3818,7 @@
         <v>1880731.5</v>
       </c>
       <c r="C17" s="13">
-        <v>161010.44</v>
+        <v>160875.05</v>
       </c>
       <c r="D17" s="13">
         <v>0</v>
@@ -3812,13 +3827,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>2041741.94</v>
+        <v>2041606.55</v>
       </c>
       <c r="G17" s="13">
-        <v>34281.57</v>
+        <v>34178.12</v>
       </c>
       <c r="H17" s="13">
-        <v>7952863.48</v>
+        <v>7934891.15</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3829,7 +3844,7 @@
         <v>1834421.59</v>
       </c>
       <c r="C18" s="13">
-        <v>161010.36</v>
+        <v>160874.97</v>
       </c>
       <c r="D18" s="13">
         <v>0</v>
@@ -3838,13 +3853,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>1995431.95</v>
+        <v>1995296.56</v>
       </c>
       <c r="G18" s="13">
-        <v>46391.7</v>
+        <v>46286.87</v>
       </c>
       <c r="H18" s="13">
-        <v>9994687.13</v>
+        <v>9976474.58</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3855,7 +3870,7 @@
         <v>1742942.17</v>
       </c>
       <c r="C19" s="13">
-        <v>161010.43</v>
+        <v>160875.04</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -3864,13 +3879,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>1903952.6</v>
+        <v>1903817.21</v>
       </c>
       <c r="G19" s="13">
-        <v>58302.34</v>
+        <v>58196.1</v>
       </c>
       <c r="H19" s="13">
-        <v>11956942.07</v>
+        <v>11938487.89</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3881,7 +3896,7 @@
         <v>1608545.74</v>
       </c>
       <c r="C20" s="13">
-        <v>161010.36</v>
+        <v>160874.97</v>
       </c>
       <c r="D20" s="13">
         <v>0</v>
@@ -3890,13 +3905,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>1769556.1</v>
+        <v>1769420.71</v>
       </c>
       <c r="G20" s="13">
-        <v>69748.83</v>
+        <v>69641.18</v>
       </c>
       <c r="H20" s="13">
-        <v>13796247</v>
+        <v>13777549.78</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3907,7 +3922,7 @@
         <v>1434541.62</v>
       </c>
       <c r="C21" s="13">
-        <v>161010.43</v>
+        <v>160875.03</v>
       </c>
       <c r="D21" s="13">
         <v>0</v>
@@ -3916,13 +3931,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="13">
-        <v>1595552.05</v>
+        <v>1595416.65</v>
       </c>
       <c r="G21" s="13">
-        <v>80478.11</v>
+        <v>80369.04</v>
       </c>
       <c r="H21" s="13">
-        <v>15472277.16</v>
+        <v>15453335.47</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -3933,7 +3948,7 @@
         <v>1225214.31</v>
       </c>
       <c r="C22" s="13">
-        <v>161010.41</v>
+        <v>160875.03</v>
       </c>
       <c r="D22" s="13">
         <v>0</v>
@@ -3942,13 +3957,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="13">
-        <v>1386224.72</v>
+        <v>1386089.34</v>
       </c>
       <c r="G22" s="13">
-        <v>90254.95</v>
+        <v>90144.46</v>
       </c>
       <c r="H22" s="13">
-        <v>16948756.83</v>
+        <v>16929569.27</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -3959,7 +3974,7 @@
         <v>985718.15</v>
       </c>
       <c r="C23" s="13">
-        <v>161010.36</v>
+        <v>160874.97</v>
       </c>
       <c r="D23" s="13">
         <v>0</v>
@@ -3968,13 +3983,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="13">
-        <v>1146728.51</v>
+        <v>1146593.12</v>
       </c>
       <c r="G23" s="13">
-        <v>98867.75</v>
+        <v>98755.82</v>
       </c>
       <c r="H23" s="13">
-        <v>18194353.09</v>
+        <v>18174918.21</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -3985,7 +4000,7 @@
         <v>721950.29</v>
       </c>
       <c r="C24" s="13">
-        <v>161010.41</v>
+        <v>160875.03</v>
       </c>
       <c r="D24" s="13">
         <v>0</v>
@@ -3994,13 +4009,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="13">
-        <v>882960.7</v>
+        <v>882825.32</v>
       </c>
       <c r="G24" s="13">
-        <v>106133.73</v>
+        <v>106020.36</v>
       </c>
       <c r="H24" s="13">
-        <v>19183447.52</v>
+        <v>19163763.89</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -4011,7 +4026,7 @@
         <v>440405.65</v>
       </c>
       <c r="C25" s="13">
-        <v>161010.36</v>
+        <v>160874.97</v>
       </c>
       <c r="D25" s="13">
         <v>0</v>
@@ -4020,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="F25" s="13">
-        <v>601416.01</v>
+        <v>601280.62</v>
       </c>
       <c r="G25" s="13">
-        <v>111903.44</v>
+        <v>111788.62</v>
       </c>
       <c r="H25" s="13">
-        <v>19896766.97</v>
+        <v>19876833.13</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -4037,7 +4052,7 @@
         <v>148016.77</v>
       </c>
       <c r="C26" s="13">
-        <v>161010.41</v>
+        <v>160875.03</v>
       </c>
       <c r="D26" s="13">
         <v>0</v>
@@ -4046,13 +4061,13 @@
         <v>0</v>
       </c>
       <c r="F26" s="13">
-        <v>309027.18</v>
+        <v>308891.8</v>
       </c>
       <c r="G26" s="13">
-        <v>116064.47</v>
+        <v>115948.19</v>
       </c>
       <c r="H26" s="13">
-        <v>20321858.62</v>
+        <v>20301673.12</v>
       </c>
     </row>
   </sheetData>
@@ -4074,7 +4089,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4979,6 +4994,26 @@
       </c>
       <c r="F51" s="12" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
